--- a/outputs/Book1_report__report.xlsx
+++ b/outputs/Book1_report__report.xlsx
@@ -7,11 +7,11 @@
   </bookViews>
   <sheets>
     <sheet name="ProjectManagerLevel" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Licence Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Allocated" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Required" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ISL" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Keystore" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Allocated" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Required" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ISL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Keystore" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Licence Summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1168,130 +1168,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>📊  Licence Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Total Lic</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Own Lic</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Lease Lic</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Annual</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Order</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Autocad</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>sp3d</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C4" s="8">
-        <f>SUM(C3:C3)</f>
-        <v/>
-      </c>
-      <c r="D4" s="8">
-        <f>SUM(D3:D3)</f>
-        <v/>
-      </c>
-      <c r="E4" s="8">
-        <f>SUM(E3:E3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="8">
-        <f>SUM(F3:F3)</f>
-        <v/>
-      </c>
-      <c r="G4" s="8">
-        <f>SUM(G3:G3)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1386,7 +1262,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1495,7 +1371,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1641,7 +1517,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1804,4 +1680,128 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>📊  Licence Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Total Lic</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Own Lic</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Lease Lic</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Autocad</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>sp3d</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C4" s="8">
+        <f>SUM(C3:C3)</f>
+        <v/>
+      </c>
+      <c r="D4" s="8">
+        <f>SUM(D3:D3)</f>
+        <v/>
+      </c>
+      <c r="E4" s="8">
+        <f>SUM(E3:E3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="8">
+        <f>SUM(F3:F3)</f>
+        <v/>
+      </c>
+      <c r="G4" s="8">
+        <f>SUM(G3:G3)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>